--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104738_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104738_W32.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2085</v>
+        <v>6.614</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8993</v>
+        <v>4.4723</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3092</v>
+        <v>2.1417</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3766</v>
+        <v>3.3754</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5471</v>
+        <v>2.5422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8295</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0879</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9761</v>
+        <v>1.9683</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2887</v>
+        <v>1.2955</v>
       </c>
       <c r="N2" t="n">
-        <v>0.571</v>
+        <v>0.574</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7177</v>
+        <v>0.7215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3545</v>
+        <v>0.7621</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4858</v>
+        <v>0.1043</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8403</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0231</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4332</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3139</v>
+        <v>6.1392</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8808</v>
+        <v>3.6892</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4331</v>
+        <v>2.45</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9813</v>
+        <v>1.979</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5613</v>
+        <v>0.5576</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42</v>
+        <v>1.4214</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0723</v>
+        <v>2.0612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9971</v>
+        <v>0.989</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0752</v>
+        <v>1.0722</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.091</v>
+        <v>-0.0822</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4358</v>
+        <v>-0.4314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3449</v>
+        <v>0.3492</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3091</v>
+        <v>1.1406</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3975</v>
+        <v>0.4294</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7066</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1979</v>
+        <v>3.9741</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8127</v>
+        <v>1.2424</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3852</v>
+        <v>2.7316</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9177</v>
+        <v>2.3597</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6153999999999999</v>
+        <v>1.5019</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5331</v>
+        <v>0.8578</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1571</v>
+        <v>1.5958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7146</v>
+        <v>1.7754</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4426</v>
+        <v>-0.1796</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2395</v>
+        <v>0.7639</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3299</v>
+        <v>-0.2734</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0905</v>
+        <v>1.0374</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4078</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7875</v>
+        <v>1.6144</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1638</v>
+        <v>0.8335</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6237</v>
+        <v>0.7809</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9318</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5732</v>
+        <v>3.9665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9091</v>
+        <v>1.4347</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6641</v>
+        <v>2.5318</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2067</v>
+        <v>2.9164</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1774</v>
+        <v>-0.6121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0293</v>
+        <v>3.5285</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9219000000000001</v>
+        <v>3.1446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.4346</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2847</v>
+        <v>-0.2282</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2554</v>
+        <v>-1.3221</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0293</v>
+        <v>1.0939</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2719</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1359</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0015</v>
+        <v>-1.0197</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7581</v>
+        <v>-0.523</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2434</v>
+        <v>-0.4967</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6369</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6369</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.368</v>
+        <v>2.0707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.906</v>
+        <v>2.649</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4619</v>
+        <v>-0.5782</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3621</v>
+        <v>1.2766</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5019</v>
+        <v>0.089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8601</v>
+        <v>1.1876</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6069</v>
+        <v>2.5089</v>
       </c>
       <c r="K6" t="n">
-        <v>1.78</v>
+        <v>1.7269</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1731</v>
+        <v>0.782</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7552</v>
+        <v>-1.2323</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.278</v>
+        <v>-1.638</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0332</v>
+        <v>0.4057</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2719</v>
+        <v>2.9592</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0059</v>
+        <v>-1.1847</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4798</v>
+        <v>-0.5138</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5261</v>
+        <v>-0.671</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.792</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0913</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9603</v>
+        <v>1.976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7588</v>
+        <v>0.2372</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2015</v>
+        <v>1.7388</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6927</v>
+        <v>1.2082</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2653</v>
+        <v>1.1749</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4274</v>
+        <v>0.0333</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1799</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1676</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3475</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8726</v>
+        <v>0.2914</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0977</v>
+        <v>0.2581</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7749</v>
+        <v>0.0333</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5903</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5903</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7685999999999999</v>
+        <v>1.4099</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2336</v>
+        <v>1.1006</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5349</v>
+        <v>0.3093</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0913</v>
+        <v>1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>0.705</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6515</v>
+        <v>1.7207</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3131</v>
+        <v>0.6272</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6616</v>
+        <v>1.0935</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2737</v>
+        <v>0.6894</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0887</v>
+        <v>0.2618</v>
       </c>
       <c r="I8" t="n">
-        <v>1.185</v>
+        <v>0.4276</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5171</v>
+        <v>-0.1888</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7342</v>
+        <v>0.1616</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7829</v>
+        <v>-0.3505</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2434</v>
+        <v>0.8782</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6455</v>
+        <v>0.1002</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4021</v>
+        <v>0.778</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8175</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9534</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5991</v>
+        <v>0.5274</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0.1136</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7348</v>
+        <v>0.4138</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7963</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6369</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6246</v>
+        <v>0.3492</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3151</v>
+        <v>-1.4551</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9397</v>
+        <v>1.8043</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0239</v>
+        <v>-0.0234</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0218</v>
+        <v>-1.0198</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9979</v>
+        <v>0.9964</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8034</v>
+        <v>0.7917</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1503</v>
+        <v>0.1444</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6531</v>
+        <v>0.6473</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8273</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1722</v>
+        <v>-1.1642</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3449</v>
+        <v>0.3492</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1925</v>
+        <v>-0.4681</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.006</v>
+        <v>-0.1282</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1864</v>
+        <v>-0.3399</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2966</v>
+        <v>-1.2973</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1592</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3878</v>
+        <v>-0.3868</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1294,22 +1294,22 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3878</v>
+        <v>-0.3868</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.418</v>
+        <v>-1.6291</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3315</v>
+        <v>-2.338</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9135</v>
+        <v>0.7089</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9853</v>
+        <v>-1.9787</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4854</v>
+        <v>-0.4803</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4999</v>
+        <v>-1.4985</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2904</v>
+        <v>-1.2924</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1383</v>
+        <v>0.1379</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4287</v>
+        <v>-1.4303</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6949</v>
+        <v>-0.6863</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6237</v>
+        <v>-0.6182</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7046</v>
+        <v>-1.9267</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0411</v>
+        <v>-1.0455</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6635</v>
+        <v>-0.8812</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2324</v>
+        <v>-4.9363</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.1687</v>
+        <v>-7.0739</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9363</v>
+        <v>2.1376</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2841</v>
+        <v>-2.2883</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7341</v>
+        <v>-2.7365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.45</v>
+        <v>0.4482</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8082</v>
+        <v>-2.8206</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2682</v>
+        <v>-2.2762</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5399</v>
+        <v>-0.5443</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5241</v>
+        <v>0.5322</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4659</v>
+        <v>-0.4603</v>
       </c>
       <c r="O13" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0396</v>
+        <v>-1.7375</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9527</v>
+        <v>-0.8389</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0869</v>
+        <v>-0.8986</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9359</v>
+        <v>18.9333</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5286</v>
+        <v>2.3468</v>
       </c>
       <c r="F14" t="n">
-        <v>16.4072</v>
+        <v>16.5864</v>
       </c>
       <c r="G14" t="n">
-        <v>9.114699999999997</v>
+        <v>9.113100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9394000000000009</v>
+        <v>0.9339000000000004</v>
       </c>
       <c r="I14" t="n">
-        <v>8.175199999999998</v>
+        <v>8.179</v>
       </c>
       <c r="J14" t="n">
-        <v>8.888100000000001</v>
+        <v>8.797199999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>6.3119</v>
+        <v>6.254100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5764</v>
+        <v>2.5431</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2264000000000003</v>
+        <v>0.3160000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.372499999999999</v>
+        <v>-5.320099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>5.599100000000001</v>
+        <v>5.636099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5439</v>
+        <v>4.5528</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1749</v>
+        <v>-18.2107</v>
       </c>
       <c r="R14" t="n">
-        <v>22.7187</v>
+        <v>22.76309999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8836999999999999</v>
+        <v>-0.8823000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4397999999999996</v>
+        <v>-0.468</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4440000000000002</v>
+        <v>-0.4143999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>6.1612</v>
+        <v>6.149900000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>12.2553</v>
+        <v>12.2284</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.093999999999999</v>
+        <v>-6.0785</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1373</v>
+        <v>5.3007</v>
       </c>
       <c r="E15" t="n">
-        <v>3.539</v>
+        <v>2.9931</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5983</v>
+        <v>2.3076</v>
       </c>
       <c r="G15" t="n">
-        <v>0.032</v>
+        <v>3.5865</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8814</v>
+        <v>0.6923</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8494</v>
+        <v>2.8942</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4142</v>
+        <v>4.6159</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0167</v>
+        <v>1.5406</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6025</v>
+        <v>3.0753</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3822</v>
+        <v>-1.0295</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1353</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2469</v>
+        <v>-0.1811</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9087</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0447</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5597</v>
+        <v>0.763</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4644</v>
+        <v>0.3851</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0953</v>
+        <v>0.3779</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7963</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1586</v>
+        <v>3.8624</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3127</v>
+        <v>2.3347</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8459</v>
+        <v>1.5277</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5901</v>
+        <v>0.0308</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6935</v>
+        <v>1.876</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8966</v>
+        <v>-1.8452</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6325</v>
+        <v>1.4025</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5501</v>
+        <v>2.006</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0824</v>
+        <v>-0.6035</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0423</v>
+        <v>-1.3717</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8566</v>
+        <v>-0.13</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1857</v>
+        <v>-1.2417</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.635</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9534</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3868</v>
+        <v>1.2868</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3216</v>
+        <v>0.2783</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.0085</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6369</v>
+        <v>1.792</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7403</v>
+        <v>2.93</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2098</v>
+        <v>2.3142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5305</v>
+        <v>0.6158</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2783</v>
+        <v>3.2762</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1473</v>
+        <v>1.146</v>
       </c>
       <c r="I17" t="n">
-        <v>2.131</v>
+        <v>2.1302</v>
       </c>
       <c r="J17" t="n">
-        <v>3.112</v>
+        <v>3.1019</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4404</v>
+        <v>1.4339</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6717</v>
+        <v>1.668</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1663</v>
+        <v>0.1743</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4594</v>
+        <v>0.4622</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6274</v>
+        <v>-0.4436</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9023</v>
+        <v>-0.7877</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2749</v>
+        <v>0.3441</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.5525</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5594</v>
+        <v>1.6555</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5408</v>
+        <v>-2.2079</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3239</v>
+        <v>0.3241</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5876</v>
+        <v>0.5861</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2636</v>
+        <v>-0.262</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2528</v>
+        <v>2.2433</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6996</v>
+        <v>1.6925</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5532</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9289</v>
+        <v>-1.9193</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.112</v>
+        <v>-1.1064</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8169</v>
+        <v>-0.8129</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1012</v>
+        <v>-0.6701</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7635</v>
+        <v>-0.6483</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3378</v>
+        <v>-0.0218</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9439</v>
+        <v>-1.6086</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2911</v>
+        <v>-1.0579</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6528</v>
+        <v>-0.5507</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5458</v>
+        <v>-0.5447</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0218</v>
+        <v>-1.0198</v>
       </c>
       <c r="I19" t="n">
-        <v>0.476</v>
+        <v>0.4751</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.944</v>
+        <v>-0.9463</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1551</v>
+        <v>-0.1566</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3982</v>
+        <v>0.4016</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2329</v>
+        <v>-0.2301</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9883</v>
+        <v>-0.6573</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.347</v>
+        <v>-0.1116</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6413</v>
+        <v>-0.5457</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0798</v>
+        <v>-2.9593</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9849</v>
+        <v>-2.8741</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0949</v>
+        <v>-0.0852</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8902</v>
+        <v>-1.8873</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0922</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7955</v>
+        <v>-1.795</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1549</v>
+        <v>-1.1573</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3111</v>
+        <v>0.3103</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.466</v>
+        <v>-1.4676</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7353</v>
+        <v>-0.73</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7352</v>
+        <v>-0.6167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5786</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0412</v>
+        <v>-0.0381</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1579</v>
+        <v>-3.4793</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9402</v>
+        <v>-2.5281</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2177</v>
+        <v>-0.9513</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.712</v>
+        <v>-3.4429</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8498</v>
+        <v>-0.9597</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1378</v>
+        <v>-2.4833</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9184</v>
+        <v>-2.0816</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9557</v>
+        <v>0.1756</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>-2.2572</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7936</v>
+        <v>-1.3613</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8941</v>
+        <v>-1.1353</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1005</v>
+        <v>-0.226</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9087</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>1.191</v>
+        <v>0.9149</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0225</v>
+        <v>0.9193</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1684</v>
+        <v>-0.0044</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1825</v>
+        <v>-1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5013</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3887</v>
+        <v>-3.5946</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0441</v>
+        <v>-4.0631</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3446</v>
+        <v>0.4685</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4471</v>
+        <v>-2.1405</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9633</v>
+        <v>0.5944</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4839</v>
+        <v>-2.7349</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.076</v>
+        <v>-1.5845</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1788</v>
+        <v>0.71</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2549</v>
+        <v>-2.2945</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3711</v>
+        <v>-0.556</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1421</v>
+        <v>-0.1155</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.229</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6816</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3631</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0447</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0138</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.395</v>
+        <v>-0.2023</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3813</v>
+        <v>0.7482</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6369</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6369</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2353</v>
+        <v>-3.7773</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4047</v>
+        <v>-1.5424</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1694</v>
+        <v>-2.2349</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1419</v>
+        <v>-1.7108</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5943000000000001</v>
+        <v>-1.8495</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7362</v>
+        <v>0.1387</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5776</v>
+        <v>-0.9215</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7146</v>
+        <v>-0.9588</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2921</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5643</v>
+        <v>-0.7893</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1203</v>
+        <v>-0.8907</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.444</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9087</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3631</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0935</v>
+        <v>0.5677</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5553</v>
+        <v>0.4294</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4618</v>
+        <v>0.1383</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0913</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0913</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7251</v>
+        <v>-5.9509</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2813</v>
+        <v>-5.8388</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4438</v>
+        <v>-0.1122</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9545</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6176</v>
+        <v>-0.6149</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3369</v>
+        <v>-0.3452</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0709</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3517</v>
+        <v>0.348</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2657</v>
+        <v>-0.2771</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0405</v>
+        <v>-1.031</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9629</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.9069</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2715</v>
+        <v>-0.4868</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4604</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8111</v>
+        <v>-0.4956</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.46</v>
+        <v>-7.5247</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.081899999999999</v>
+        <v>-7.9796</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6219</v>
+        <v>0.4549</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6474</v>
+        <v>-5.6442</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2961</v>
+        <v>-1.2928</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3513</v>
+        <v>-4.3515</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.053</v>
+        <v>-5.0593</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1458</v>
+        <v>-1.1484</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.9072</v>
+        <v>-3.911</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5944</v>
+        <v>-0.5849</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1503</v>
+        <v>-0.1444</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.444</v>
+        <v>-0.4405</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3233</v>
+        <v>1.2577</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6061</v>
+        <v>0.7219</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.9359</v>
+        <v>-17.3541</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.4073</v>
+        <v>-16.5865</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.528599999999999</v>
+        <v>-0.7676999999999998</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.114599999999999</v>
+        <v>-9.113</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9392000000000006</v>
+        <v>-0.9341000000000002</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.175400000000002</v>
+        <v>-8.178899999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.226399999999999</v>
+        <v>-0.3160000000000007</v>
       </c>
       <c r="K26" t="n">
-        <v>5.3726</v>
+        <v>5.3201</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.5989</v>
+        <v>-5.636100000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.888100000000001</v>
+        <v>-8.797099999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.3118</v>
+        <v>-6.254</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.5762</v>
+        <v>-2.543</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.543699999999999</v>
+        <v>-4.5528</v>
       </c>
       <c r="Q26" t="n">
-        <v>-22.7187</v>
+        <v>-22.7632</v>
       </c>
       <c r="R26" t="n">
-        <v>18.175</v>
+        <v>18.2105</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8838999999999998</v>
+        <v>2.4615</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4437999999999997</v>
+        <v>0.4142999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4397</v>
+        <v>2.0472</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.1615</v>
+        <v>-6.1499</v>
       </c>
       <c r="W26" t="n">
-        <v>6.0939</v>
+        <v>6.0784</v>
       </c>
       <c r="X26" t="n">
-        <v>-12.2554</v>
+        <v>-12.2284</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104738_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104738_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.0785</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104738_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-12.2284</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
